--- a/outputs/Block5B_Senate_2026_Race_Stability.xlsx
+++ b/outputs/Block5B_Senate_2026_Race_Stability.xlsx
@@ -58,43 +58,43 @@
     <t>Role</t>
   </si>
   <si>
+    <t>Maine</t>
+  </si>
+  <si>
+    <t>Alaska</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>New Hampshire</t>
+  </si>
+  <si>
     <t>Michigan</t>
   </si>
   <si>
-    <t>Maine</t>
+    <t>Ohio</t>
+  </si>
+  <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>Iowa</t>
   </si>
   <si>
     <t>Georgia</t>
   </si>
   <si>
-    <t>New Hampshire</t>
-  </si>
-  <si>
-    <t>North Carolina</t>
-  </si>
-  <si>
-    <t>Ohio</t>
-  </si>
-  <si>
-    <t>Texas</t>
-  </si>
-  <si>
-    <t>Montana</t>
-  </si>
-  <si>
-    <t>Alaska</t>
-  </si>
-  <si>
     <t>Nebraska</t>
   </si>
   <si>
-    <t>Iowa</t>
+    <t>D</t>
   </si>
   <si>
     <t>R</t>
-  </si>
-  <si>
-    <t>D</t>
   </si>
   <si>
     <t>Sensitivity diagnostic; never a Senate seat quota</t>
@@ -507,34 +507,34 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>-0.03080609054227335</v>
+        <v>1.25229017498787</v>
       </c>
       <c r="C2" t="s">
         <v>25</v>
       </c>
       <c r="D2">
-        <v>-0.8841566174724429</v>
+        <v>-1.506144668308227</v>
       </c>
       <c r="E2">
-        <v>-0.1672601165464371</v>
+        <v>0.328403642916468</v>
       </c>
       <c r="F2">
-        <v>3.721583798244428</v>
+        <v>4.388637398267414</v>
       </c>
       <c r="G2">
-        <v>-6.772500854639566</v>
+        <v>-9.075435312273683</v>
       </c>
       <c r="H2">
-        <v>2.40808133434199</v>
+        <v>1.750772399588051</v>
       </c>
       <c r="I2">
-        <v>9.180582188981557</v>
+        <v>10.82620771186173</v>
       </c>
       <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
         <v>2</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
       </c>
       <c r="L2">
         <v>60</v>
@@ -551,40 +551,40 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>0.3438631074494971</v>
+        <v>1.686016982113115</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3">
-        <v>-1.312082529786079</v>
+        <v>-1.221547391213839</v>
       </c>
       <c r="E3">
-        <v>-1.165492557175527</v>
+        <v>0.6424537334128565</v>
       </c>
       <c r="F3">
-        <v>3.412515124976018</v>
+        <v>4.281138390930596</v>
       </c>
       <c r="G3">
-        <v>-6.602644263031961</v>
+        <v>-8.655528146621872</v>
       </c>
       <c r="H3">
-        <v>2.231447846393365</v>
+        <v>1.497081958893681</v>
       </c>
       <c r="I3">
-        <v>8.834092109425328</v>
+        <v>10.15261010551555</v>
       </c>
       <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
         <v>2</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
       </c>
       <c r="L3">
         <v>60</v>
       </c>
       <c r="M3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="s">
         <v>27</v>
@@ -595,34 +595,34 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>6.957784224064383</v>
+        <v>-0.7843797050406334</v>
       </c>
       <c r="C4" t="s">
         <v>26</v>
       </c>
       <c r="D4">
-        <v>5.643768123659367</v>
+        <v>-3.100991117501406</v>
       </c>
       <c r="E4">
-        <v>6.077348066298342</v>
+        <v>-1.516711512570621</v>
       </c>
       <c r="F4">
-        <v>3.824057317294319</v>
+        <v>4.864648380335356</v>
       </c>
       <c r="G4">
-        <v>-0.4846225547925229</v>
+        <v>-11.11754838992667</v>
       </c>
       <c r="H4">
-        <v>9.848596397380661</v>
+        <v>1.856335754640838</v>
       </c>
       <c r="I4">
-        <v>10.33321895217318</v>
+        <v>12.97388414456751</v>
       </c>
       <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>4</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
       </c>
       <c r="L4">
         <v>80</v>
@@ -639,28 +639,28 @@
         <v>17</v>
       </c>
       <c r="B5">
-        <v>6.826841239737266</v>
+        <v>7.757545040113389</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5">
-        <v>5.536771498445193</v>
+        <v>5.601396453171871</v>
       </c>
       <c r="E5">
-        <v>6.065400843881861</v>
+        <v>7.247328067624592</v>
       </c>
       <c r="F5">
-        <v>3.813047822510088</v>
+        <v>4.635283520068727</v>
       </c>
       <c r="G5">
-        <v>-0.5927564181068075</v>
+        <v>-2.348561440178459</v>
       </c>
       <c r="H5">
         <v>9.69704849010213</v>
       </c>
       <c r="I5">
-        <v>10.28980490820894</v>
+        <v>12.04560993028059</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -683,28 +683,28 @@
         <v>18</v>
       </c>
       <c r="B6">
-        <v>5.016399172114285</v>
+        <v>3.322364192499973</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6">
-        <v>3.718272295211226</v>
+        <v>1.392297270608908</v>
       </c>
       <c r="E6">
-        <v>4.337089984632125</v>
+        <v>3.203230148048448</v>
       </c>
       <c r="F6">
-        <v>3.628737823236699</v>
+        <v>4.785124955322779</v>
       </c>
       <c r="G6">
-        <v>-1.977759998573099</v>
+        <v>-6.995912889582467</v>
       </c>
       <c r="H6">
-        <v>7.750472589792061</v>
+        <v>5.027582767314211</v>
       </c>
       <c r="I6">
-        <v>9.728232588365159</v>
+        <v>12.02349565689668</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -727,34 +727,34 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>-1.160073261865543</v>
+        <v>3.027335204854857</v>
       </c>
       <c r="C7" t="s">
         <v>25</v>
       </c>
       <c r="D7">
-        <v>-2.77301820592738</v>
+        <v>0.3217350511822473</v>
       </c>
       <c r="E7">
-        <v>-2.827852922905387</v>
+        <v>2.032823649239744</v>
       </c>
       <c r="F7">
-        <v>3.469784010094946</v>
+        <v>4.322752131399832</v>
       </c>
       <c r="G7">
-        <v>-7.991268636298971</v>
+        <v>-7.176472161128217</v>
       </c>
       <c r="H7">
-        <v>1.119500130174437</v>
+        <v>3.498315625809795</v>
       </c>
       <c r="I7">
-        <v>9.110768766473408</v>
+        <v>10.67478778693801</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <v>80</v>
@@ -771,37 +771,37 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>-3.703052659673662</v>
+        <v>8.15573551212689</v>
       </c>
       <c r="C8" t="s">
         <v>25</v>
       </c>
       <c r="D8">
-        <v>-5.242536055496659</v>
+        <v>5.581654157228656</v>
       </c>
       <c r="E8">
-        <v>-5.491928930119531</v>
+        <v>6.943821333383879</v>
       </c>
       <c r="F8">
-        <v>3.57091112328249</v>
+        <v>4.138913238437175</v>
       </c>
       <c r="G8">
-        <v>-10.38858325292123</v>
+        <v>-1.695802107663628</v>
       </c>
       <c r="H8">
-        <v>-0.8942661756970125</v>
+        <v>8.458498023715421</v>
       </c>
       <c r="I8">
-        <v>9.494317077224222</v>
+        <v>10.15430013137905</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
@@ -815,28 +815,28 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>-9.436014161597619</v>
+        <v>-28.19535625398524</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9">
-        <v>-11.96132553882961</v>
+        <v>-29.7588816391178</v>
       </c>
       <c r="E9">
-        <v>-11.59999999999999</v>
+        <v>-29.22220350797864</v>
       </c>
       <c r="F9">
-        <v>3.315905304077201</v>
+        <v>6.40944545551198</v>
       </c>
       <c r="G9">
-        <v>-17.00475432417813</v>
+        <v>-39.67221627274333</v>
       </c>
       <c r="H9">
-        <v>-7.845302386032147</v>
+        <v>-21.88581315216757</v>
       </c>
       <c r="I9">
-        <v>9.159451938145983</v>
+        <v>17.78640312057576</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -859,28 +859,28 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>-3.284649066643004</v>
+        <v>-4.13103634630254</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10">
-        <v>-4.928956408434331</v>
+        <v>-6.690922212101691</v>
       </c>
       <c r="E10">
-        <v>-5.077702110704545</v>
+        <v>-4.748170664481129</v>
       </c>
       <c r="F10">
-        <v>3.469208120534087</v>
+        <v>4.756525853848467</v>
       </c>
       <c r="G10">
-        <v>-10.06626130089964</v>
+        <v>-14.69916668017758</v>
       </c>
       <c r="H10">
-        <v>-0.9895833333333286</v>
+        <v>-2.410596026490069</v>
       </c>
       <c r="I10">
-        <v>9.076677967566312</v>
+        <v>12.28857065368751</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -903,34 +903,34 @@
         <v>23</v>
       </c>
       <c r="B11">
-        <v>-8.505893509862281</v>
+        <v>10.33409373772884</v>
       </c>
       <c r="C11" t="s">
         <v>25</v>
       </c>
       <c r="D11">
-        <v>-10.97952853648557</v>
+        <v>8.166596743803989</v>
       </c>
       <c r="E11">
-        <v>-10.40000000000001</v>
+        <v>9.764152809749833</v>
       </c>
       <c r="F11">
-        <v>3.282828727826491</v>
+        <v>4.588567775436318</v>
       </c>
       <c r="G11">
-        <v>-16.02966504416926</v>
+        <v>0.383899469915236</v>
       </c>
       <c r="H11">
-        <v>-6.979829876754016</v>
+        <v>12.31460748976793</v>
       </c>
       <c r="I11">
-        <v>9.049835167415248</v>
+        <v>11.93070801985269</v>
       </c>
       <c r="J11">
+        <v>5</v>
+      </c>
+      <c r="K11">
         <v>0</v>
-      </c>
-      <c r="K11">
-        <v>5</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -947,28 +947,28 @@
         <v>24</v>
       </c>
       <c r="B12">
-        <v>-3.236981791669953</v>
+        <v>-6.011641417509835</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12">
-        <v>-4.973008116339102</v>
+        <v>-9.155711900886308</v>
       </c>
       <c r="E12">
-        <v>-5.020649128521597</v>
+        <v>-7.215793060150304</v>
       </c>
       <c r="F12">
-        <v>3.391845381096703</v>
+        <v>4.371509117880124</v>
       </c>
       <c r="G12">
-        <v>-10.10199173231504</v>
+        <v>-16.77952132936703</v>
       </c>
       <c r="H12">
-        <v>-1.396070320579113</v>
+        <v>-5.941181113156134</v>
       </c>
       <c r="I12">
-        <v>8.705921411735925</v>
+        <v>10.83834021621089</v>
       </c>
       <c r="J12">
         <v>0</v>
